--- a/光伏配储项目/电价数据/2026/下海北开关站.xlsx
+++ b/光伏配储项目/电价数据/2026/下海北开关站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5099</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.72309</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56488</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5184299999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45481</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44949</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45467</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26828</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.2165</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25982</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07798999999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06397</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05273</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03346</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05467</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03904999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04577000000000001</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.01073</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08628</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01706</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00362</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14527</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21302</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23619</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21515</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11772</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00238</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00675</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.15897</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.01294</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.19318</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22438</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.01672</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.03621</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.1243</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19637</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.00276</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.24116</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.01434</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45882</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52885</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.48759</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.76762</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61572</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.5193300000000001</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.15698</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5924700000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5449299999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.5039100000000001</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50651</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.61933</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.57572</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.43854</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.34926</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62659</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.43441</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75837</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.7853</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.61282</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54635</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52788</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50774</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51681</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5119</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47749</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42554</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52907</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65654</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.75413</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44314</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45025</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.09109</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04255</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.2223</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>-0.02091</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>-0.01738</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.01424</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.00382</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.5939500000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.00523</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.01332</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27675</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.58797</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.01385</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.00662</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>-0.00925</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.2708</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.23392</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.16162</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23622</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.26438</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23531</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27424</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.44233</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.27486</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.48388</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.71072</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.64576</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.74361</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8499500000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.44802</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.8337100000000001</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43849</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59909</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.31151</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.43876</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47423</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.27131</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.23442</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.22896</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27714</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.00842</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.03458</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.03669</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.01211</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.04096</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.04179</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.03788</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.03267</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.04015999999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.01292</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.02277</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.04708</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.04368</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.07360999999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21976</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.15254</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.21029</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.1973</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24928</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.27193</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.28807</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.25457</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.2256</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.07121</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28614</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.48369</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.00838</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5043299999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34414</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.26897</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27266</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47948</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27266</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.27924</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.27843</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26077</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.1949</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10843</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11309</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08220000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.24967</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21133</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13425</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21708</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04046</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04151</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06113</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.27192</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17516</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.004849999999999999</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21256</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03271</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.05018</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07811</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19908</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.16471</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20219</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.14984</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19381</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14114</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.19788</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22596</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.27855</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25855</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.46915</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29605</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25425</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29224</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27503</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27331</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27603</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26046</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04077</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04513</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04028</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04003</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04266</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04496</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04346</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04548</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04665999999999999</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04715</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04803</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04653</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04771</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04694</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04596</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.0481</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04654999999999999</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04808</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04654</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04732</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04639</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04876</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05157</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14712</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03762</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09889000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66447</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10244</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04264</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04588</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04505</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03238000000000001</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04064</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10697</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00112</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.0412</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04112</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04364</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04352</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04101</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04042</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04323</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04027</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03890999999999999</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04395</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04368</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04211</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03994</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04263</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04641</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2024</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14486</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27146</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3378</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32306</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27358</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27374</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17441</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16067</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17331</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14964</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16136</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16075</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23969</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21617</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22877</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27206</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28349</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.01035</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.27915</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.10022</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15728</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.19295</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.2739</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50751</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79108</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.4978</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78087</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92003</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92835</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.90773</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31996</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.93086</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63897</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.2297</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8899</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.58157</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37454</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.57462</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.82821</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53076</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.8104199999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.80722</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8813799999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.89342</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.52812</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43282</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44479</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48986</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2519</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.88009</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55179</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6664</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54941</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.51051</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46128</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42952</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45207</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45327</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42243</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41397</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58975</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59687</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60202</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.64415</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45494</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44745</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86526</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.67469</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.65887</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.77625</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.23792</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43435</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.01936</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35328</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02764</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.50031</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.50496</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.62491</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.69972</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41585</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.45196</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5146900000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16475</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20123</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.05902</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.28276</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.27417</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27491</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24371</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44696</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59766</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8897699999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35796</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13631</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71209</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8062</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65122</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59112</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42366</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42831</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43441</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42384</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.02364</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27715</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.26436</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.26737</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.00271</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.26283</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.00101</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.23836</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23926</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.11862</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.25137</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.28626</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.24934</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.11158</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.25738</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26876</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48975</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.43306</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.60902</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46581</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.68262</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46678</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4396600000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42568</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32659</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40231</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.03193</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.03954999999999999</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23729</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14661</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14932</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15628</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14483</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14245</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14489</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14384</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25906</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14552</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26892</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14343</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05422</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11484</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11376</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14773</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14261</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14787</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45146</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44186</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44131</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44626</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44551</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40432</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35074</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.46221</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47039</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42548</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41749</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.07739</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.00248</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.25146</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.25167</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.24402</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>-0.01002</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.18572</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.09518</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>-0.01169</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.15041</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.01074</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>-0.01088</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.20252</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.18121</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-0.00629</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.20039</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.21109</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>-0.01147</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.19446</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.18312</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.21504</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>-0.01082</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.21225</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>-0.01136</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.01246</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44857</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.46181</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24973</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42793</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.51658</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36065</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.24085</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03238000000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25524</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.21172</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18524</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24512</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28666</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27177</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25383</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50826</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7809700000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.45401</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.4715299999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.44157</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41796</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.01639</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29095</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>-0.01694</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34466</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>-0.03689</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.7448899999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41736</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42953</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6495</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.87952</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48815</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.49067</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46051</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34508</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26155</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13653</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29151</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19538</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24666</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.03025</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13131</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.02116</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23804</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28746</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24841</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.00411</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14519</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.01903</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23569</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23816</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41795</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.71369</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.66374</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6946</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46228</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.5861900000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47848</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45452</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46028</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48202</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43062</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49358</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45855</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42163</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41146</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40199</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41157</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50098</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45099</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41872</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42011</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42725</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.17561</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.00617</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.15514</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04427</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03712</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.02059</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.18449</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.1093</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.01245</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.03938000000000001</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41608</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48628</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50618</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50847</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.43002</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.63189</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.75387</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.77767</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8770800000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.61068</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.57745</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.98062</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.89498</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6940599999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.7603</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.52327</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.52904</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.5225599999999999</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.51813</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.44351</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.60138</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.44847</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47167</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4925</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.46491</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43863</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.48862</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.41338</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.42413</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15913</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27528</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03972</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45263</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46362</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01465</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18508</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40386</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41275</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36266</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44384</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.09515000000000001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25016</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23571</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24712</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25227</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.04203</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.04194</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.15047</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05972</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17708</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25966</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.04274</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14887</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.06084000000000001</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.01292</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.12353</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.04796</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.03876</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.02627</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.15098</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.02343</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.00641</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.03761</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.00941</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36446</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35152</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19074</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.18414</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13006</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.14827</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.05048</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00144</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04369</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.13714</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.18967</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22206</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22265</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.22775</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.23792</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26496</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24761</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24075</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23213</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.24786</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23424</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25279</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24147</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.25894</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24675</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.25969</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27424</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.25701</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21582</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21421</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18305</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.07898000000000001</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.04368</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.22897</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.15046</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15195</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15238</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.01667</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23152</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21449</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.19889</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15483</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.12911</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15402</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.1863</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.10598</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12042</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.18924</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.15668</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.20867</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.18034</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.16835</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.21968</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.16731</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.21867</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.28886</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.22597</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20827</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21537</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.12799</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.4387200000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.18736</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>-0.00318</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.16893</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16561</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.00558</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02844</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18581</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26491</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.07845999999999999</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.00929</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23568</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25354</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28323</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.20673</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32633</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10561</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25679</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.12363</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24649</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>-0.00082</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26984</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.19081</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14332</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10766</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33221</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.23956</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26249</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.26603</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25962</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28458</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26254</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26497</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26809</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26371</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24944</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28301</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.03894</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.04548</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42933</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.52555</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.01282</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.55175</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.48055</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45779</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>1.06646</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5025299999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42961</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.47766</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40307</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36903</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46804</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21258</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17928</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23599</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.28763</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26325</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26834</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27891</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46712</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5609700000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.54935</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46248</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5522899999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46606</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5335700000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52124</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7987799999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8412500000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55371</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44505</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37693</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27244</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.28995</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26683</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.26572</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26142</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25375</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24689</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.28952</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.23725</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23599</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25305</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.18926</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.21119</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.0009300000000000001</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.03355</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.01025</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01359</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.13531</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01019</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02263</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.02074</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23562</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.0139</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03126</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02217</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01879</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.10405</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06570000000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11895</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13947</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16715</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22264</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18109</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.18862</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20705</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.24868</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4197</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38092</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.79215</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27478</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27044</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26085</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23203</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22595</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19503</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.19947</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21457</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>-0.01269</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.01338</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.01535</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.01597</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03607</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07653</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.03379</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.004940000000000001</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01425</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04413</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.007650000000000001</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.00831</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.00216</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15506</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.01355</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.009140000000000001</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>-0.005809999999999999</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.00404</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>-0.01331</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.00856</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.01029</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.05889</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22772</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.17997</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.23029</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.52842</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40882</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43158</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.40245</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.4050299999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5121599999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23011</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18421</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.16973</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11133</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14574</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17183</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.15887</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08544</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10227</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04785</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.06827</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03702</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03779</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03853</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03741</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04499</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05055</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.05916</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03396</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.0559</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07044</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11229</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.13743</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.15982</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14143</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08754000000000001</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04586999999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21295</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09331999999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.08954000000000001</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18492</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.12763</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.13911</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14386</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.17843</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.19716</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.19823</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21095</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25365</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.2575</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27161</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41378</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42114</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49844</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41859</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.4441000000000001</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4161</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41508</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38204</v>
       </c>
     </row>
   </sheetData>
